--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="474">
   <si>
     <t>Result</t>
   </si>
@@ -1674,6 +1674,69 @@
   </si>
   <si>
     <t>Fri Sep 18 02:25:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 20:16:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Sep 22 23:28:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 23 22:40:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 17:56:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 17:59:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:36:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:40:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:42:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:46:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:48:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 17:03:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 17:04:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 17:05:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 18:49:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 18:58:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:26:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:27:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:28:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:32:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:33:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:34:33 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -4236,7 +4299,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4266,7 +4329,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>11</v>
@@ -4290,10 +4353,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s" s="0">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>11</v>
@@ -4461,7 +4524,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4607,7 +4670,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4747,7 +4810,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -4887,7 +4950,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5027,7 +5090,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5283,7 +5346,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5399,7 +5462,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="12" t="s">
@@ -5638,7 +5701,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5851,10 +5914,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsACH.xlsx
+++ b/KatalonData/ABPTestData/PaymentsACH.xlsx
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="478">
   <si>
     <t>Result</t>
   </si>
@@ -1737,6 +1737,18 @@
   </si>
   <si>
     <t>Fri Sep 25 20:34:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:42:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:43:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:44:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:45:04 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -4071,10 +4083,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
